--- a/artfynd/A 40245-2023 artfynd.xlsx
+++ b/artfynd/A 40245-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40245-2023 artfynd.xlsx
+++ b/artfynd/A 40245-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94934160</v>
+        <v>94934202</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408760.3137404274</v>
+        <v>408799</v>
       </c>
       <c r="R2" t="n">
-        <v>7019850.259950343</v>
+        <v>7019920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,32 +746,18 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94934559</v>
+        <v>94934459</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408892.109164839</v>
+        <v>408848</v>
       </c>
       <c r="R3" t="n">
-        <v>7020112.024009729</v>
+        <v>7020051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +847,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grankvist och sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94934202</v>
+        <v>94934567</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408799.2391855348</v>
+        <v>408892</v>
       </c>
       <c r="R4" t="n">
-        <v>7019919.808121556</v>
+        <v>7020112</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,19 +953,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94934567</v>
+        <v>94934512</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408892.109164839</v>
+        <v>408842</v>
       </c>
       <c r="R5" t="n">
-        <v>7020112.024009729</v>
+        <v>7020042</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,19 +1054,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94934459</v>
+        <v>94934559</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408847.5770301935</v>
+        <v>408892</v>
       </c>
       <c r="R6" t="n">
-        <v>7020051.188038221</v>
+        <v>7020112</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,24 +1155,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grankvist och sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94934512</v>
+        <v>94934160</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,26 +1196,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408841.9190464077</v>
+        <v>408760</v>
       </c>
       <c r="R7" t="n">
-        <v>7020042.348603209</v>
+        <v>7019850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,19 +1257,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1273,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1378,6 +1288,111 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94934959</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sågbäcken O, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>408499</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7019881</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40245-2023 artfynd.xlsx
+++ b/artfynd/A 40245-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934202</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934567</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934559</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934160</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,8 +1428,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934959</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>